--- a/output/pdf_financials_xlsx/TOI.xlsx
+++ b/output/pdf_financials_xlsx/TOI.xlsx
@@ -1188,19 +1188,19 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>75.32599999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>136.772</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>179.059</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>206.157</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>326.686</v>
       </c>
     </row>
     <row r="35">
@@ -1232,19 +1232,19 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>75.32599999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>136.772</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>179.059</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>206.157</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>326.686</v>
       </c>
     </row>
     <row r="37">
@@ -1496,19 +1496,19 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>129.694</v>
+        <v>54.368</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>212.586</v>
+        <v>75.81399999999999</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>279.146</v>
+        <v>100.087</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>306.679</v>
+        <v>100.522</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>448.564</v>
+        <v>121.878</v>
       </c>
     </row>
     <row r="49">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/TOI.xlsx
+++ b/output/pdf_financials_xlsx/TOI.xlsx
@@ -1071,19 +1071,19 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>109.663</v>
+        <v>85.06</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>134.944</v>
+        <v>107.078</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>151.71</v>
+        <v>121.124</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>169.587</v>
+        <v>135.499</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>204.28</v>
+        <v>162.554</v>
       </c>
     </row>
     <row r="29">
@@ -1093,19 +1093,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2090.969</v>
+        <v>-2115.572</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>239.362</v>
+        <v>211.496</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>296.476</v>
+        <v>265.89</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>353.061</v>
+        <v>318.973</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>312.509</v>
+        <v>270.783</v>
       </c>
     </row>
     <row r="30">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-281.5964370990962</v>
+        <v>-284.9097894931054</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>26.11180988806357</v>
+        <v>23.07193014800132</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>26.35405471953549</v>
+        <v>23.63523391228056</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>27.26630328173967</v>
+        <v>24.63374475426725</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>20.13197174261194</v>
+        <v>17.44396386785561</v>
       </c>
     </row>
     <row r="31">
@@ -2645,19 +2645,19 @@
         </is>
       </c>
       <c r="B100" s="3" t="n">
-        <v>0</v>
+        <v>85.06</v>
       </c>
       <c r="C100" s="3" t="n">
-        <v>0</v>
+        <v>107.078</v>
       </c>
       <c r="D100" s="3" t="n">
-        <v>0</v>
+        <v>121.124</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>0</v>
+        <v>135.499</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>162.554</v>
       </c>
     </row>
     <row r="101">
@@ -3233,13 +3233,13 @@
         <v>0</v>
       </c>
       <c r="D126" s="3" t="n">
-        <v>0</v>
+        <v>-1.814</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>0</v>
+        <v>-80.489</v>
       </c>
       <c r="F126" s="3" t="n">
-        <v>0</v>
+        <v>-3.692</v>
       </c>
     </row>
     <row r="127">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
@@ -7090,7 +7090,11 @@
           <t>Dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -8148,7 +8152,11 @@
           <t>Dividends paid to non-controlling interests</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -8382,7 +8390,11 @@
           <t>Dividends to non-controlling interests</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>CashDividendsPaid</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -9370,7 +9382,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -10171,7 +10183,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E176" s="5" t="n">

--- a/output/pdf_financials_xlsx/TOI.xlsx
+++ b/output/pdf_financials_xlsx/TOI.xlsx
@@ -1990,19 +1990,19 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>16.234</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>18.824</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>20.614</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>23.629</v>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0</v>
+        <v>30.915</v>
       </c>
     </row>
     <row r="71">
@@ -2012,19 +2012,19 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>16.234</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>18.824</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>20.614</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>23.629</v>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0</v>
+        <v>30.915</v>
       </c>
     </row>
     <row r="72">
@@ -2100,19 +2100,19 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>180.622</v>
+        <v>164.388</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>278.328</v>
+        <v>259.504</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>215.758</v>
+        <v>195.144</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>283.235</v>
+        <v>259.606</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>442.729</v>
+        <v>411.814</v>
       </c>
     </row>
     <row r="76">
@@ -2166,19 +2166,19 @@
         </is>
       </c>
       <c r="B78" s="3" t="n">
-        <v>0</v>
+        <v>38.955</v>
       </c>
       <c r="C78" s="3" t="n">
-        <v>0</v>
+        <v>36.634</v>
       </c>
       <c r="D78" s="3" t="n">
-        <v>0</v>
+        <v>41.524</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>0</v>
+        <v>53.188</v>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0</v>
+        <v>67.43600000000001</v>
       </c>
     </row>
     <row r="79">
@@ -2188,19 +2188,19 @@
         </is>
       </c>
       <c r="B79" s="3" t="n">
-        <v>0</v>
+        <v>38.955</v>
       </c>
       <c r="C79" s="3" t="n">
-        <v>0</v>
+        <v>36.634</v>
       </c>
       <c r="D79" s="3" t="n">
-        <v>0</v>
+        <v>41.524</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>0</v>
+        <v>53.188</v>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0</v>
+        <v>67.43600000000001</v>
       </c>
     </row>
     <row r="80">
@@ -2209,30 +2209,20 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.03895140549437209</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.08283878715818059</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.07346810407409947</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>0.1022161899629415</v>
+      </c>
+      <c r="F80" s="3" t="n">
+        <v>0.09024724833569617</v>
       </c>
     </row>
     <row r="81">
@@ -2330,19 +2320,19 @@
         </is>
       </c>
       <c r="B85" s="3" t="n">
-        <v>273.893</v>
+        <v>234.938</v>
       </c>
       <c r="C85" s="3" t="n">
-        <v>256.869</v>
+        <v>220.235</v>
       </c>
       <c r="D85" s="3" t="n">
-        <v>274.266</v>
+        <v>232.742</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>304.285</v>
+        <v>251.097</v>
       </c>
       <c r="F85" s="3" t="n">
-        <v>716.266</v>
+        <v>648.83</v>
       </c>
     </row>
     <row r="86">
@@ -2931,19 +2921,19 @@
         </is>
       </c>
       <c r="B113" s="3" t="n">
-        <v>0</v>
+        <v>-241.507</v>
       </c>
       <c r="C113" s="3" t="n">
-        <v>0</v>
+        <v>-153.828</v>
       </c>
       <c r="D113" s="3" t="n">
-        <v>0</v>
+        <v>-113.846</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>0</v>
+        <v>-112.952</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>0</v>
+        <v>-311.003</v>
       </c>
     </row>
     <row r="114">
@@ -4325,7 +4315,11 @@
           <t>Lease obligations (note 13)</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>16.234</v>
       </c>
@@ -4543,7 +4537,11 @@
           <t>Lease obligations (note 13)</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -5389,7 +5387,11 @@
           <t>Lease obligations (note 12)</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -5539,7 +5541,11 @@
           <t>Lease obligations (note 12)</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E54" t="inlineStr">
         <is>
           <t>-</t>
@@ -6054,7 +6060,11 @@
           <t>Lease obligations</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LongTermCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
         <v>38.955</v>
       </c>
@@ -6179,7 +6189,11 @@
           <t>Net income (loss)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="n">
         <v>-2222.233</v>
       </c>
@@ -7209,7 +7223,11 @@
           <t>Acquisition of businesses (note 4)</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>PurchaseOfBusiness</t>
+        </is>
+      </c>
       <c r="E98" s="5" t="n">
         <v>-241.507</v>
       </c>
